--- a/all_sim/gemini_realset.xlsx
+++ b/all_sim/gemini_realset.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.2375</v>
+        <v>0.61875</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.15833333333333333</v>
+        <v>0.5391666666666667</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.15833333333333333</v>
+        <v>0.5391666666666667</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.15833333333333333</v>
+        <v>0.5391666666666667</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.15833333333333333</v>
+        <v>0.5391666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.0925925925925926</v>
+        <v>0.5168845315904139</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.0925925925925926</v>
+        <v>0.5168845315904139</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.13</v>
+        <v>0.565</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.11111111111111109</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.13888888888888892</v>
+        <v>0.5012626262626263</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.5464285714285714</v>
+        <v>0.7550324675324676</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.4004464285714286</v>
+        <v>0.680992445054945</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.4577380952380952</v>
+        <v>0.6574404761904762</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.38822751322751325</v>
+        <v>0.563678974005061</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.38822751322751325</v>
+        <v>0.6449334287449042</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.6844796711057304</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.39797619047619043</v>
+        <v>0.6334143247462919</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.39107142857142857</v>
+        <v>0.6751275510204081</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.39107142857142857</v>
+        <v>0.6228084415584415</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.3575892857142857</v>
+        <v>0.6606128246753247</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.42237762237762233</v>
+        <v>0.6792739175717899</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.2845117845117845</v>
+        <v>0.5912354840926269</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.22525252525252526</v>
+        <v>0.5616058544629974</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.1772727272727273</v>
+        <v>0.5261363636363636</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.3395833333333333</v>
+        <v>0.6059618794326241</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.3395833333333333</v>
+        <v>0.6059618794326241</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.3395833333333333</v>
+        <v>0.6059618794326241</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.5806159420289855</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.5806159420289855</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.3168560606060606</v>
+        <v>0.5945982430689878</v>
       </c>
     </row>
     <row r="5">
@@ -504,28 +504,28 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="G5" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.10069444444444445</v>
+        <v>0.5503472222222222</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.10069444444444445</v>
+        <v>0.5503472222222222</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.10069444444444445</v>
+        <v>0.524031432748538</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.06712962962962964</v>
+        <v>0.5335648148148148</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.06712962962962964</v>
+        <v>0.5335648148148148</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.1541005291005291</v>
+        <v>0.5770502645502645</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.1541005291005291</v>
+        <v>0.5770502645502645</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.03935185185185186</v>
+        <v>0.5196759259259259</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.03935185185185186</v>
+        <v>0.5196759259259259</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.03935185185185186</v>
+        <v>0.5196759259259259</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,34 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.1561157796451914</v>
+        <v>0.5131228248875308</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.16013071895424838</v>
+        <v>0.5151302945420593</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.1723901098901099</v>
+        <v>0.5407405094905094</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.16758241758241757</v>
+        <v>0.5123626373626374</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.034929356357927786</v>
+        <v>0.3447374054516912</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.06928571428571428</v>
+        <v>0.43770408163265306</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.2074175824175824</v>
+        <v>0.551469985238642</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.17460317460317462</v>
+        <v>0.5425254678986022</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.21982758620689655</v>
+        <v>0.5736819090454772</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>0.12797619047619047</v>
+        <v>0.34834828481155494</v>
       </c>
     </row>
     <row r="8">
@@ -609,34 +609,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.875</v>
+        <v>0.9263888888888889</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.2829545454545454</v>
+        <v>0.6289772727272727</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.22727272727272727</v>
+        <v>0.6008158508158508</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.30584415584415586</v>
+        <v>0.6272810522810522</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.040259740259740266</v>
+        <v>0.49687405617638175</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.030844155844155847</v>
+        <v>0.4558982683982684</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.030844155844155847</v>
+        <v>0.4558982683982684</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.03131313131313132</v>
+        <v>0.4815656565656566</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.03131313131313132</v>
+        <v>0.4924007517030773</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.03131313131313132</v>
+        <v>0.4668760778516876</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +646,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.05972222222222222</v>
+        <v>0.514709595959596</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.04079861111111111</v>
+        <v>0.4703993055555556</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.03819444444444444</v>
+        <v>0.4682497645951036</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.035243055555555555</v>
+        <v>0.4486560105363984</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.45707614942528735</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.0421875</v>
+        <v>0.4509183114035088</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.04666666666666667</v>
+        <v>0.4356140350877193</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.4367559523809524</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.4367559523809524</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.052083333333333336</v>
+        <v>0.4367559523809524</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +683,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.8569444444444445</v>
+        <v>0.9284722222222223</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.8569444444444445</v>
+        <v>0.9284722222222223</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.8569444444444445</v>
+        <v>0.9284722222222223</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.49537037037037035</v>
+        <v>0.7476851851851851</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.49537037037037035</v>
+        <v>0.7476851851851851</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.49537037037037035</v>
+        <v>0.7476851851851851</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.45092592592592595</v>
+        <v>0.725462962962963</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.09398148148148147</v>
+        <v>0.5469907407407407</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.12175925925925925</v>
+        <v>0.5608796296296297</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.5444444444444444</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.5367647058823529</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.475</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.493421052631579</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.493421052631579</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.25</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="12">

--- a/all_sim/gemini_realset.xlsx
+++ b/all_sim/gemini_realset.xlsx
@@ -331,16 +331,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18"/>
   <cols>
     <col width="17.6" min="1" max="1" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="2" max="2" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="3" max="3" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="4" max="4" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="5" max="5" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="6" max="6" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="2" max="2" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="3" max="3" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="4" max="4" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="5" max="5" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="6" max="6" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="7" max="7" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="8" max="8" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="9" max="9" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="10" max="10" bestFit="1" customWidth="1"/>
-    <col width="24.200000000000003" min="11" max="11" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="8" max="8" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="9" max="9" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="10" max="10" bestFit="1" customWidth="1"/>
+    <col width="25.3" min="11" max="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -350,34 +350,34 @@
         </is>
       </c>
       <c r="B1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="C1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="D1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="E1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="F1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="G1" s="0" t="n">
-        <v>0.61875</v>
+        <v>0.2375</v>
       </c>
       <c r="H1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
       <c r="I1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
       <c r="J1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
       <c r="K1" s="0" t="n">
-        <v>0.5391666666666667</v>
+        <v>0.14566666666666667</v>
       </c>
     </row>
     <row r="2">
@@ -387,34 +387,34 @@
         </is>
       </c>
       <c r="B2" s="0" t="n">
-        <v>0.5168845315904139</v>
+        <v>0.08714596949891068</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0.5168845315904139</v>
+        <v>0.08714596949891068</v>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0.565</v>
+        <v>0.13</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0.4888888888888889</v>
+        <v>0.09629629629629628</v>
       </c>
       <c r="F2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
       <c r="G2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
       <c r="H2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
       <c r="I2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
       <c r="J2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
       <c r="K2" s="0" t="n">
-        <v>0.5012626262626263</v>
+        <v>0.11994949494949499</v>
       </c>
     </row>
     <row r="3">
@@ -424,34 +424,34 @@
         </is>
       </c>
       <c r="B3" s="0" t="n">
-        <v>0.7550324675324676</v>
+        <v>0.5265584415584414</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0.680992445054945</v>
+        <v>0.3850446428571429</v>
       </c>
       <c r="D3" s="0" t="n">
-        <v>0.6574404761904762</v>
+        <v>0.39234693877551025</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>0.563678974005061</v>
+        <v>0.2869507706464228</v>
       </c>
       <c r="F3" s="0" t="n">
-        <v>0.6449334287449042</v>
+        <v>0.35004120045103654</v>
       </c>
       <c r="G3" s="0" t="n">
-        <v>0.6844796711057304</v>
+        <v>0.4071453793381759</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0.6334143247462919</v>
+        <v>0.34578259172521464</v>
       </c>
       <c r="I3" s="0" t="n">
-        <v>0.6751275510204081</v>
+        <v>0.3751093294460641</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>0.6228084415584415</v>
+        <v>0.33418831168831165</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>0.6606128246753247</v>
+        <v>0.34458603896103895</v>
       </c>
     </row>
     <row r="4">
@@ -461,34 +461,34 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0.6792739175717899</v>
+        <v>0.3954173486088379</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0.5912354840926269</v>
+        <v>0.25547996976568405</v>
       </c>
       <c r="D4" s="0" t="n">
-        <v>0.5616058544629974</v>
+        <v>0.20226757369614512</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>0.5261363636363636</v>
+        <v>0.1551136363636364</v>
       </c>
       <c r="F4" s="0" t="n">
-        <v>0.6059618794326241</v>
+        <v>0.2962322695035461</v>
       </c>
       <c r="G4" s="0" t="n">
-        <v>0.6059618794326241</v>
+        <v>0.2962322695035461</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>0.6059618794326241</v>
+        <v>0.2962322695035461</v>
       </c>
       <c r="I4" s="0" t="n">
-        <v>0.5806159420289855</v>
+        <v>0.2536231884057971</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>0.5806159420289855</v>
+        <v>0.2536231884057971</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>0.5945982430689878</v>
+        <v>0.27640635074145714</v>
       </c>
     </row>
     <row r="5">
@@ -504,28 +504,28 @@
         <v>1.0</v>
       </c>
       <c r="D5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="H5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I5" s="0" t="n">
         <v>1.0</v>
       </c>
       <c r="J5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K5" s="0" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
@@ -535,34 +535,34 @@
         </is>
       </c>
       <c r="B6" s="0" t="n">
-        <v>0.5503472222222222</v>
+        <v>0.10069444444444445</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>0.5503472222222222</v>
+        <v>0.10069444444444445</v>
       </c>
       <c r="D6" s="0" t="n">
-        <v>0.524031432748538</v>
+        <v>0.09539473684210527</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>0.5335648148148148</v>
+        <v>0.06712962962962964</v>
       </c>
       <c r="F6" s="0" t="n">
-        <v>0.5335648148148148</v>
+        <v>0.06712962962962964</v>
       </c>
       <c r="G6" s="0" t="n">
-        <v>0.5770502645502645</v>
+        <v>0.1541005291005291</v>
       </c>
       <c r="H6" s="0" t="n">
-        <v>0.5770502645502645</v>
+        <v>0.1541005291005291</v>
       </c>
       <c r="I6" s="0" t="n">
-        <v>0.5196759259259259</v>
+        <v>0.03935185185185186</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>0.5196759259259259</v>
+        <v>0.03935185185185186</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>0.5196759259259259</v>
+        <v>0.03935185185185186</v>
       </c>
     </row>
     <row r="7">
@@ -572,34 +572,36 @@
         </is>
       </c>
       <c r="B7" s="0" t="n">
-        <v>0.5131228248875308</v>
+        <v>0.13584100306789382</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0.5151302945420593</v>
+        <v>0.13933452168746288</v>
       </c>
       <c r="D7" s="0" t="n">
-        <v>0.5407405094905094</v>
+        <v>0.1567182817182817</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>0.5123626373626374</v>
+        <v>0.14364207221350078</v>
       </c>
       <c r="F7" s="0" t="n">
-        <v>0.3447374054516912</v>
+        <v>0.022862851434280004</v>
       </c>
       <c r="G7" s="0" t="n">
-        <v>0.43770408163265306</v>
+        <v>0.05585276967930029</v>
       </c>
       <c r="H7" s="0" t="n">
-        <v>0.551469985238642</v>
+        <v>0.18574708873216336</v>
       </c>
       <c r="I7" s="0" t="n">
-        <v>0.5425254678986022</v>
+        <v>0.15896706941483063</v>
       </c>
       <c r="J7" s="0" t="n">
-        <v>0.5736819090454772</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0.34834828481155494</v>
+        <v>0.20389805097451275</v>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>failed</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -609,34 +611,34 @@
         </is>
       </c>
       <c r="B8" s="0" t="n">
-        <v>0.9263888888888889</v>
+        <v>0.8555555555555555</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>0.6289772727272727</v>
+        <v>0.27588068181818176</v>
       </c>
       <c r="D8" s="0" t="n">
-        <v>0.6008158508158508</v>
+        <v>0.22144522144522144</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>0.6272810522810522</v>
+        <v>0.29015984015984014</v>
       </c>
       <c r="F8" s="0" t="n">
-        <v>0.49687405617638175</v>
+        <v>0.038387194201147695</v>
       </c>
       <c r="G8" s="0" t="n">
-        <v>0.4558982683982684</v>
+        <v>0.02717223252937539</v>
       </c>
       <c r="H8" s="0" t="n">
-        <v>0.4558982683982684</v>
+        <v>0.02717223252937539</v>
       </c>
       <c r="I8" s="0" t="n">
-        <v>0.4815656565656566</v>
+        <v>0.029178145087236006</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>0.4924007517030773</v>
+        <v>0.029856706600892655</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>0.4668760778516876</v>
+        <v>0.028258191672825828</v>
       </c>
     </row>
     <row r="9">
@@ -646,34 +648,34 @@
         </is>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.514709595959596</v>
+        <v>0.05791245791245791</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0.4703993055555556</v>
+        <v>0.03671875</v>
       </c>
       <c r="D9" s="0" t="n">
-        <v>0.4682497645951036</v>
+        <v>0.03431026365348399</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>0.4486560105363984</v>
+        <v>0.03038194444444444</v>
       </c>
       <c r="F9" s="0" t="n">
-        <v>0.45707614942528735</v>
+        <v>0.04489942528735632</v>
       </c>
       <c r="G9" s="0" t="n">
-        <v>0.4509183114035088</v>
+        <v>0.03626644736842106</v>
       </c>
       <c r="H9" s="0" t="n">
-        <v>0.4356140350877193</v>
+        <v>0.03847953216374269</v>
       </c>
       <c r="I9" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.042782738095238096</v>
       </c>
       <c r="J9" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.042782738095238096</v>
       </c>
       <c r="K9" s="0" t="n">
-        <v>0.4367559523809524</v>
+        <v>0.042782738095238096</v>
       </c>
     </row>
     <row r="10">
@@ -683,34 +685,34 @@
         </is>
       </c>
       <c r="B10" s="0" t="n">
-        <v>0.9284722222222223</v>
+        <v>0.8569444444444445</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>0.9284722222222223</v>
+        <v>0.8569444444444445</v>
       </c>
       <c r="D10" s="0" t="n">
-        <v>0.9284722222222223</v>
+        <v>0.8569444444444445</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>0.7476851851851851</v>
+        <v>0.49537037037037035</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.7476851851851851</v>
+        <v>0.49537037037037035</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.7476851851851851</v>
+        <v>0.49537037037037035</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0.725462962962963</v>
+        <v>0.45092592592592595</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>0.5469907407407407</v>
+        <v>0.09398148148148147</v>
       </c>
       <c r="J10" s="0" t="n">
-        <v>0.5608796296296297</v>
+        <v>0.12175925925925925</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>0.5444444444444444</v>
+        <v>0.08888888888888889</v>
       </c>
     </row>
     <row r="11">
@@ -720,34 +722,34 @@
         </is>
       </c>
       <c r="B11" s="0" t="n">
-        <v>0.5367647058823529</v>
+        <v>0.20588235294117646</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0.475</v>
+        <v>0.175</v>
       </c>
       <c r="D11" s="0" t="n">
-        <v>0.493421052631579</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>0.493421052631579</v>
+        <v>0.1842105263157895</v>
       </c>
       <c r="F11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="G11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="I11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="J11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
       <c r="K11" s="0" t="n">
-        <v>0.425</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
